--- a/reports/一级子公司B_现金流量表_2026-11.xlsx
+++ b/reports/一级子公司B_现金流量表_2026-11.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>46757880</v>
+        <v>45237257</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>536510520</v>
+        <v>520673434</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>985718</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>11292265</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>491484</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>5639084</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>245651</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2823469</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>197209</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2255639</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>146983</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1693833</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>98812</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1128133</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>73401</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>846597</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>49417</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>564314</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>122433</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1410352</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>61980</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>709308</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>39025</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>448264</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>149865</v>
+        <v>145514</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1719585</v>
+        <v>1670666</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>899190</v>
+        <v>874315</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>10317510</v>
+        <v>10009889</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>47806935</v>
+        <v>48769199</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>23978400</v>
+        <v>23171025</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>275133600</v>
+        <v>267088790</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>329131</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3763204</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>245240</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2819989</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>164123</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1882189</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>123001</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1409725</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>81801</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>941142</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>61997</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>708546</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>8492350</v>
+        <v>8209002</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>97443150</v>
+        <v>94648741</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3197120</v>
+        <v>3119257</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>36684480</v>
+        <v>35606584</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1798380</v>
+        <v>1737356</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>20635020</v>
+        <v>20034777</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>37466250</v>
+        <v>37241933</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>10340685</v>
+        <v>11527266</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>61800</v>
+        <v>59776</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>679800</v>
+        <v>660393</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>618000</v>
+        <v>597009</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>6798000</v>
+        <v>6601356</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>370800</v>
+        <v>361746</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>4078800</v>
+        <v>3960125</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>679800</v>
+        <v>656785</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6180000</v>
+        <v>6018736</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>67980000</v>
+        <v>66031171</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>927000</v>
+        <v>898458</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>10197000</v>
+        <v>9893772</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4326000</v>
+        <v>4200525</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>47586000</v>
+        <v>46233277</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>144200</v>
+        <v>139331</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1586200</v>
+        <v>1540547</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6324200</v>
+        <v>6158067</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5644400</v>
+        <v>-5501282</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1236000</v>
+        <v>1196771</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>13596000</v>
+        <v>13193006</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2060000</v>
+        <v>2000811</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>22660000</v>
+        <v>21983851</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2060000</v>
+        <v>1996051</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>22660000</v>
+        <v>22015937</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>61800</v>
+        <v>60200</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>679800</v>
+        <v>659577</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>3357800</v>
+        <v>3257782</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>1648000</v>
+        <v>1607855</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>18128000</v>
+        <v>17595002</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>1648000</v>
+        <v>1592072</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>18128000</v>
+        <v>17600900</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>288400</v>
+        <v>281255</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3172400</v>
+        <v>3080574</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>247200</v>
+        <v>240535</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2719200</v>
+        <v>2641536</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>36050</v>
+        <v>34976</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>396550</v>
+        <v>384731</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>1972450</v>
+        <v>1924086</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1385350</v>
+        <v>1333696</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>6081635</v>
+        <v>7359680</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>6081635</v>
+        <v>7359680</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
